--- a/InputData/trans/BVTStL/Boolean Veh Types Subject to LCFS.xlsx
+++ b/InputData/trans/BVTStL/Boolean Veh Types Subject to LCFS.xlsx
@@ -1,38 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24931"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27231"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-india\InputData\trans\BVTStL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\robbie\Dropbox (Energy Innovation)\My Documents\Energy Policy Solutions\US\Models\eps-us\InputData\trans\BVTStL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CC0452BA-DF5F-456C-BE82-85A55BE60C54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B748A387-264B-4ED0-9400-910230BD852C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="735" yWindow="720" windowWidth="26730" windowHeight="20460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="BVTStL" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029" iterate="1" iterateDelta="1.0000000000000001E-5"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>Source:</t>
   </si>
@@ -64,71 +53,44 @@
     <t>freight</t>
   </si>
   <si>
-    <t>BVTStL Boolean Vehicle Types Subject to LCFS</t>
+    <t>The LCFS percentage set (both the BAU LCFS and the user-specified</t>
+  </si>
+  <si>
+    <t>Additional LCFS Percentage policy lever) will only refer to the fuel</t>
+  </si>
+  <si>
+    <t>used by the vehicle types specified in this variable.  Other vehicle</t>
+  </si>
+  <si>
+    <t>types will be unaffected by the LCFS.</t>
+  </si>
+  <si>
+    <t>California Air Resources Board</t>
+  </si>
+  <si>
+    <t>Low Carbon Fuel Standard: Final Regulation Order</t>
+  </si>
+  <si>
+    <t>https://www.arb.ca.gov/regact/2015/lcfs2015/lcfsfinalregorder.pdf</t>
+  </si>
+  <si>
+    <t>Page 15</t>
   </si>
   <si>
     <t>(Boolean)</t>
   </si>
   <si>
-    <t>The LCFS percentage set (both the BAU LCFS and the user-specified</t>
-  </si>
-  <si>
-    <t>Additional LCFS Percentage policy lever) will only refer to the fuel</t>
-  </si>
-  <si>
-    <t>used by the vehicle types specified in this variable.  Other vehicle</t>
-  </si>
-  <si>
-    <t>types will be unaffected by the LCFS.</t>
-  </si>
-  <si>
-    <t>India National Biofuel blending requirement</t>
-  </si>
-  <si>
-    <t>Ministry of Petroleum and Natural Gas/ Press Information Bureau</t>
-  </si>
-  <si>
-    <t>National Policy on Biofuel</t>
-  </si>
-  <si>
-    <t>https://pib.gov.in/PressReleasePage.aspx?PRID=1575404</t>
-  </si>
-  <si>
-    <t>India's biofuel blending targets apply only to on-road vehicles.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">While there are news articles referring to an aviation-biofuel policy in the </t>
-  </si>
-  <si>
-    <t>include aircrafts in the BAU as yet as the policy is not officially announced.</t>
-  </si>
-  <si>
-    <t>Biofuel in Aviation - India test flight/probable new Bio-ATF policy</t>
-  </si>
-  <si>
-    <t>SpiceJet operates India's first biofuel-powered flight from Dehradun to Delhi</t>
-  </si>
-  <si>
-    <t>https://economictimes.indiatimes.com/industry/transportation/airlines-/-aviation/spicejet-operates-indias-first-biojet-fuel-flight/articleshow/65560105.cms</t>
-  </si>
-  <si>
-    <t>Economic Times/quotes Nitin Gadkari (Minister of Road Transport &amp; Highways, Shipping)</t>
-  </si>
-  <si>
-    <t>offing, and test flights by commercial airlines using blended fuel - we don't</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sources are listed for reference. </t>
-  </si>
-  <si>
-    <t>We therefore exclude railways.</t>
+    <t>Based on the California LCFS, we choose to exempt aircraft.</t>
+  </si>
+  <si>
+    <t>BVTStL BAU Vehicle Types Subject to LCFS</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -144,27 +106,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.249977111117893"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -176,11 +124,10 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -189,11 +136,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -210,9 +154,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -250,9 +194,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -285,26 +229,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -337,26 +264,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -530,122 +440,75 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="59.140625" customWidth="1"/>
-    <col min="4" max="4" width="58.5703125" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B4" s="2">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
         <v>17</v>
       </c>
-      <c r="D4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B5" s="2">
-        <v>2019</v>
-      </c>
-      <c r="D5" s="2">
-        <v>2018</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B7" s="5" t="s">
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>19</v>
       </c>
-      <c r="D7" s="5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>28</v>
-      </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="B7" r:id="rId1" xr:uid="{69B01CCB-AD3F-4B58-A467-05348C4CD5DC}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId2"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -664,7 +527,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>8</v>
@@ -711,10 +574,10 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -725,7 +588,7 @@
         <v>1</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">

--- a/InputData/trans/BVTStL/Boolean Veh Types Subject to LCFS.xlsx
+++ b/InputData/trans/BVTStL/Boolean Veh Types Subject to LCFS.xlsx
@@ -1,34 +1,126 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28224"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\robbie\Dropbox (Energy Innovation)\My Documents\Energy Policy Solutions\US\Models\eps-us\InputData\trans\BVTStL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Khushi.Parakh\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B748A387-264B-4ED0-9400-910230BD852C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{4D18F061-FCD4-4102-BD59-F3DAAAB1FBE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{80D92A64-220D-4CDA-803E-4054E82EBF2A}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="720" windowWidth="26730" windowHeight="20460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="BVTStL" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="26">
+  <si>
+    <t>BVTStL BAU Vehicle Types Subject to LCFS</t>
+  </si>
   <si>
     <t>Source:</t>
   </si>
   <si>
+    <t>Increasing India's National Biofuel blending requirement</t>
+  </si>
+  <si>
+    <t>MoCA encouraging usage of Sustainable Aviation Fuel (SAF)</t>
+  </si>
+  <si>
+    <t>Ministry of Petroleum and Natural Gas/ Press Information Bureau</t>
+  </si>
+  <si>
+    <t>Ministry of Civil Aviation/ Press Information Bureau</t>
+  </si>
+  <si>
+    <t>National Policy on Biofuel (amended in 2022), Ethanol Blended Petrol Programme</t>
+  </si>
+  <si>
+    <t>Press Release: Press Information Bureau</t>
+  </si>
+  <si>
     <t>Notes</t>
   </si>
   <si>
+    <t>The LCFS percentage set (both the BAU LCFS and the user-specified</t>
+  </si>
+  <si>
+    <t>Additional LCFS Percentage policy lever) will only refer to the fuel</t>
+  </si>
+  <si>
+    <t>used by the vehicle types specified in this variable.  Other vehicle</t>
+  </si>
+  <si>
+    <t>types will be unaffected by the LCFS.</t>
+  </si>
+  <si>
+    <t>India's biofuel blending targets apply only to on-road vehicles.</t>
+  </si>
+  <si>
+    <r>
+      <t>We therefore exclude railways</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (which has anyway been ~94% electrified)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>We include aircrafts in the BAU as the SAF policy has been officially announced.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sources are listed for reference. </t>
+  </si>
+  <si>
+    <t>(Boolean)</t>
+  </si>
+  <si>
+    <t>passenger</t>
+  </si>
+  <si>
+    <t>freight</t>
+  </si>
+  <si>
     <t>LDVs</t>
   </si>
   <si>
@@ -45,52 +137,13 @@
   </si>
   <si>
     <t>motorbikes</t>
-  </si>
-  <si>
-    <t>passenger</t>
-  </si>
-  <si>
-    <t>freight</t>
-  </si>
-  <si>
-    <t>The LCFS percentage set (both the BAU LCFS and the user-specified</t>
-  </si>
-  <si>
-    <t>Additional LCFS Percentage policy lever) will only refer to the fuel</t>
-  </si>
-  <si>
-    <t>used by the vehicle types specified in this variable.  Other vehicle</t>
-  </si>
-  <si>
-    <t>types will be unaffected by the LCFS.</t>
-  </si>
-  <si>
-    <t>California Air Resources Board</t>
-  </si>
-  <si>
-    <t>Low Carbon Fuel Standard: Final Regulation Order</t>
-  </si>
-  <si>
-    <t>https://www.arb.ca.gov/regact/2015/lcfs2015/lcfsfinalregorder.pdf</t>
-  </si>
-  <si>
-    <t>Page 15</t>
-  </si>
-  <si>
-    <t>(Boolean)</t>
-  </si>
-  <si>
-    <t>Based on the California LCFS, we choose to exempt aircraft.</t>
-  </si>
-  <si>
-    <t>BVTStL BAU Vehicle Types Subject to LCFS</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -106,13 +159,49 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBFBFBF"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -124,20 +213,28 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -440,75 +537,114 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D19"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
+  <cols>
+    <col min="2" max="2" width="69.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="50.85546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="B4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="B5" s="5">
+        <v>2024</v>
+      </c>
+      <c r="D5" s="7">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="B6" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="15">
+      <c r="B7" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B4" s="2">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
+    <row r="18" spans="1:1">
+      <c r="A18" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
+    <row r="19" spans="1:1">
+      <c r="A19" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>19</v>
-      </c>
-    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D6" r:id="rId1" display="https://pib.gov.in/PressReleaseIframePage.aspx?PRID=1909435" xr:uid="{29C81A81-6713-4AEC-9073-1678EE8CE8FF}"/>
+    <hyperlink ref="B7" r:id="rId2" display="https://pib.gov.in/PressReleaseIframePage.aspx?PRID=2043042" xr:uid="{BFCB77C5-173D-40D0-B7E3-5AB30839E68B}"/>
+    <hyperlink ref="D7" r:id="rId3" xr:uid="{5D0FC3CD-3918-4691-BDCA-2955C4DDAD68}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId4"/>
 </worksheet>
 </file>
 
@@ -518,27 +654,27 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="14.140625" customWidth="1"/>
     <col min="2" max="2" width="15.140625" customWidth="1"/>
     <col min="3" max="3" width="13.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C1" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -547,9 +683,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -558,31 +694,31 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5">
         <v>0</v>
       </c>
-      <c r="C4">
+      <c r="C5">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -591,9 +727,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -605,4 +741,175 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A251C7805F896F47A4F48569C73A0799" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7abd873f26c83d98889b6bc5171c7cdd">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="295384f30983e71c631053ca9b14fb23" ns2:_="">
+    <xsd:import namespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="10" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="11" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C04CC747-4A97-48FF-8909-40B832D39C0A}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4958FF5B-4995-49FB-95CF-EA121895DA4D}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A30361CE-12A7-4AC0-95B1-FF60E08EEE6B}"/>
 </file>